--- a/Employee_Reports_wi52/Miguelito Costelo Mainit Q0434.xlsx
+++ b/Employee_Reports_wi52/Miguelito Costelo Mainit Q0434.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -790,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1735,11 +1735,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1784,11 +1784,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1919,11 +1919,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1968,11 +1968,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2017,11 +2017,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2066,11 +2066,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2115,11 +2115,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2262,11 +2262,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2290,20 +2290,20 @@
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>418</v>
+        <v>726</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7776</v>
+        <v>7768</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7881</v>
+        <v>7873</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7886</v>
+        <v>7878</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7886</v>
+        <v>7878</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
